--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T12:22:36+00:00</t>
+    <t>2026-09-17T12:59:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:59:08+00:00</t>
+    <t>2026-09-28T13:01:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T13:01:57+00:00</t>
+    <t>2026-09-28T14:15:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T14:15:25+00:00</t>
+    <t>2026-09-28T14:29:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T14:29:01+00:00</t>
+    <t>2026-09-28T14:57:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T14:57:10+00:00</t>
+    <t>2026-09-29T08:00:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T08:00:45+00:00</t>
+    <t>2026-09-29T11:55:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T11:55:38+00:00</t>
+    <t>2026-10-08T14:23:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T07:30:19+00:00</t>
+    <t>2026-10-13T07:53:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
